--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 02/NKSX_100_RIFD_250226.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 02/NKSX_100_RIFD_250226.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67F33A2-0211-4F9A-83A3-D2F6C3C043B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A4E678-73B9-4408-87A8-694105637DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -499,68 +499,68 @@
     <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -986,66 +986,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="42" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="44"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="45" t="s">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="46"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="44"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="45" t="s">
+      <c r="A3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="46"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="44"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="47" t="s">
+      <c r="A4" s="37"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="46"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="32"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="30"/>
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -1154,40 +1154,40 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28" t="s">
+      <c r="B13" s="48"/>
+      <c r="C13" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28" t="s">
+      <c r="D13" s="48"/>
+      <c r="E13" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28" t="s">
+      <c r="F13" s="48"/>
+      <c r="G13" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="28"/>
+      <c r="H13" s="48"/>
     </row>
     <row r="14" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29" t="s">
+      <c r="B14" s="47"/>
+      <c r="C14" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29" t="s">
+      <c r="D14" s="47"/>
+      <c r="E14" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29" t="s">
+      <c r="F14" s="47"/>
+      <c r="G14" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="29"/>
+      <c r="H14" s="47"/>
     </row>
     <row r="15" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13"/>
@@ -1240,22 +1240,22 @@
       <c r="H19" s="13"/>
     </row>
     <row r="20" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28" t="s">
+      <c r="B20" s="48"/>
+      <c r="C20" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28" t="s">
+      <c r="D20" s="48"/>
+      <c r="E20" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28" t="s">
+      <c r="F20" s="48"/>
+      <c r="G20" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="28"/>
+      <c r="H20" s="48"/>
     </row>
     <row r="21" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1281,24 +1281,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="D3:H3"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="D4:H4"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G20:H20"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
